--- a/AAII_Financials/Quarterly/NLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
   <si>
     <t>NLY</t>
   </si>
@@ -656,530 +656,542 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="28" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="29" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>910700</v>
+      </c>
+      <c r="E8" s="3">
         <v>363900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1076100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>903900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>157200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>244500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>503100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>227100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>41900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>536300</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P8" s="3">
         <v>227300</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R8" s="3">
+      <c r="R8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S8" s="3">
         <v>161400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1090300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2172100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>544300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>617000</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X8" s="3">
+      <c r="X8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y8" s="3">
         <v>1984600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1004100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1163000</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AC8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD8" s="3">
         <v>1909900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>82500</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF8" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AH8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI8" s="3">
         <v>1005700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1105600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1758200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1129700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>694600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>290500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>693600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2088600</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>928300</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E9" s="3">
         <v>16600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>16500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>15100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>14600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>14100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>11600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>11200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>671500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>400500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>170500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>74900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>61800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>50400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>61000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>76000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>94600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>115100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>689500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>503500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>620100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>766900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>750200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>647700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>586800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>501000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>442700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>367400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>318700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>268900</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>222300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>198400</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>183400</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>174200</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>892900</v>
+      </c>
+      <c r="E10" s="3">
         <v>347300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1059600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>888800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>142600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>230400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>491400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>214200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>29300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>524000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-350600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-516800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>218400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-787500</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S10" s="3">
         <v>-239100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>919800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2097200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>482500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>566600</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="X10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y10" s="3">
         <v>1908600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>909500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1047900</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AC10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD10" s="3">
         <v>1289800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-684400</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AH10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI10" s="3">
         <v>504700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>662900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1390800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>811000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>425700</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>68200</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>495200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1905200</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>754100</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1222,8 +1234,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1344,8 +1357,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1466,8 +1482,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1510,41 +1529,41 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>13000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>24000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>16500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>14000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>249600</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
@@ -1552,8 +1571,8 @@
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
@@ -1564,8 +1583,8 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
+      <c r="AI14" s="3">
+        <v>0</v>
       </c>
       <c r="AJ14" s="3" t="s">
         <v>8</v>
@@ -1573,68 +1592,71 @@
       <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AL14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM14" s="3" t="s">
-        <v>8</v>
+      <c r="AL14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM14" s="3">
+        <v>0</v>
       </c>
       <c r="AN14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO14" s="3">
-        <v>0</v>
+      <c r="AO14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3">
         <v>-72600</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E15" s="3">
         <v>9600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>9100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>9200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>9300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>6900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>7300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>7000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>5100</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1710,8 +1732,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1751,252 +1776,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>76000</v>
+      </c>
+      <c r="E17" s="3">
         <v>69100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>67700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>65400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>64600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>62200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>55600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>56900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>57500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>50800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>50100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>49500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>51800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>48700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>734800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>439700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>203600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>121600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>119200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>102200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>117800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>233800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>139000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>137700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>992200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>680400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>700800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>836500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>828600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>737100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>667300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>627500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>506500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>429900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>378000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>326000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>276300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>252300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>238800</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>199300</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>834700</v>
+      </c>
+      <c r="E18" s="3">
         <v>294700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1008400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>838400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>92600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>182400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>447400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>170200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-15600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>485500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-389500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-556700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>175500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-828300</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="3">
         <v>-278300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>886700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2050500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>425100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>514800</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y18" s="3">
         <v>1750800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>865100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1025300</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD18" s="3">
         <v>1209100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-754000</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF18" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AH18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI18" s="3">
         <v>378200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>599100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1328300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>751700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>368600</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>14200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>441300</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1849800</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>729000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2039,41 +2071,42 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3">
         <v>5800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>31800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>43800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-36000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>94000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-18700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>21200</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
@@ -2086,8 +2119,8 @@
       <c r="Q20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
+      <c r="R20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S20" s="3">
         <v>0</v>
@@ -2101,11 +2134,11 @@
       <c r="V20" s="3">
         <v>0</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X20" s="3">
-        <v>0</v>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y20" s="3">
         <v>0</v>
@@ -2113,20 +2146,20 @@
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>8</v>
+      <c r="AA20" s="3">
+        <v>0</v>
       </c>
       <c r="AB20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
+      <c r="AC20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>8</v>
+      <c r="AE20" s="3">
+        <v>0</v>
       </c>
       <c r="AF20" s="3" t="s">
         <v>8</v>
@@ -2134,8 +2167,8 @@
       <c r="AG20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
+      <c r="AH20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI20" s="3">
         <v>0</v>
@@ -2161,130 +2194,136 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>844900</v>
+      </c>
+      <c r="E21" s="3">
         <v>298600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1018100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>843000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>69900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>147800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>490700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>83300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>12300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>471100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-384000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-549400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>182400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-823200</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="3">
         <v>-273600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>893100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2055200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>428600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>518100</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y21" s="3">
         <v>1759200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>878300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1036600</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD21" s="3">
         <v>1216600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-746500</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI21" s="3">
         <v>429100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>606200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1334100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>758000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>375500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>22000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>448400</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1857500</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>737600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2327,8 +2366,8 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2405,252 +2444,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>834700</v>
+      </c>
+      <c r="E23" s="3">
         <v>289000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1010200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>835200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>60800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>138600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>483500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>76200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>464200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-389500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-556700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>175500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-828300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-886900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-278300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>886700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2050400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>425100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>514800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-289700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1750800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>865100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1025300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2808600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3666900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1209100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-754100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1782300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-846700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-2253800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>378200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>599100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1328300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>751700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>368700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>14200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>441400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1849700</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>729000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1500</v>
-      </c>
-      <c r="E24" s="3">
-        <v>-7800</v>
       </c>
       <c r="F24" s="3">
         <v>-7800</v>
       </c>
       <c r="G24" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>10400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-6100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>11900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>12400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>14300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>11000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-4300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>23400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>26500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-6800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-13500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>9700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-24600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-26700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-6900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-5900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-7200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>5000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>1200</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2771,252 +2819,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>827800</v>
+      </c>
+      <c r="E26" s="3">
         <v>290500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1018000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>843100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>60400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>130300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>473100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>82400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-8800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>465200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-391200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-569100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>161200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-839300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-886800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-274000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>863300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2023900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>418500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>521500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-294800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1751100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>878600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1015500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2784000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3640200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1209700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-747200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1776400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-849300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2254900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>385400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>595900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1327700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>746800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>367300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>14500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>440400</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1848500</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>730900</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>781600</v>
+      </c>
+      <c r="E27" s="3">
         <v>242000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>971100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>791300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>19800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>87100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>443300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>24800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-46600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>425800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-440900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-599100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>131300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-876100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-918300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-302100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>839800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1995400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>388600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>492400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-322500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1723900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>841700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>980200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2855100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3675800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1174200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-783200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1808800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-881600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-2287400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>353900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>564500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1294000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>714600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>337200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-8800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>417000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1825100</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>708400</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3137,8 +3194,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3259,8 +3319,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3381,8 +3444,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3503,41 +3569,44 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-31800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-43800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>36000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-94000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>18700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-21200</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
@@ -3550,8 +3619,8 @@
       <c r="Q32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
+      <c r="R32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S32" s="3">
         <v>0</v>
@@ -3565,11 +3634,11 @@
       <c r="V32" s="3">
         <v>0</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X32" s="3">
-        <v>0</v>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y32" s="3">
         <v>0</v>
@@ -3577,20 +3646,20 @@
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>8</v>
+      <c r="AA32" s="3">
+        <v>0</v>
       </c>
       <c r="AB32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
+      <c r="AC32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>8</v>
+      <c r="AE32" s="3">
+        <v>0</v>
       </c>
       <c r="AF32" s="3" t="s">
         <v>8</v>
@@ -3598,8 +3667,8 @@
       <c r="AG32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
+      <c r="AH32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI32" s="3">
         <v>0</v>
@@ -3625,130 +3694,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>822700</v>
+      </c>
+      <c r="E33" s="3">
         <v>282700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1013500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>832400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>57100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>124200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>482100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>66400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>462900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-403700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-562200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>167000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-844300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-918300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-302100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>839800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1995400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>388600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>492400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-322500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1723900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>841700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>980200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2855100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3675800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1174200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-783200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1808800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-881600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-2287400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>353900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>564500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1294000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>714600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>337200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-8800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>417000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1825100</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>708400</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3869,257 +3944,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>822700</v>
+      </c>
+      <c r="E35" s="3">
         <v>282700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1013500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>832400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>57100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>124200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>482100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>66400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>462900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-403700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-562200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>167000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-844300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-918300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-302100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>839800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1995400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>388600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>492400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-322500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1723900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>841700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>980200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2855100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3675800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1174200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-783200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1808800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-881600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-2287400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>353900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>564500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1294000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>714600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>337200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-8800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>417000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1825100</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>708400</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4162,8 +4246,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4206,175 +4291,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>365500</v>
+      </c>
+      <c r="E41" s="3">
         <v>366700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>354800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>320300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>267100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>296900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>285100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>324200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>320600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>298300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>275900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>374600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>176900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>156000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1576700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1466200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>853900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>955800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1342100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1046300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1380500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1122800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1243700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1240000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1393900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2823500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1850700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1793900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1982300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1522600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1735700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1082700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1135300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>984300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>706600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>867800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>700700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>819400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1539700</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>2382200</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>114800</v>
+      </c>
+      <c r="E42" s="3">
         <v>428600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>149900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>82900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>149700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>67300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>225400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>59100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>187900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>203800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>162600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>549800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>457100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>400100</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4450,130 +4539,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>46488900</v>
+      </c>
+      <c r="E43" s="3">
         <v>43136400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>38015900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>34666000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>32709500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>29164300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>28790600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>25177000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>21732800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>20141300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>19593600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>15449700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>14204700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13373200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1212400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2416400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>734300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>654000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>237600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>277300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>264500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>404600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>284000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>335200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1047200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1342000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>454700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>677000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>446300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1965200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>426100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1614100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>345500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>372100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>324800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>633200</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>273000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>621000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>321900</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>754400</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4616,8 +4711,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4694,8 +4789,11 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4738,8 +4836,8 @@
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -4816,53 +4914,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>49515900</v>
+      </c>
+      <c r="E46" s="3">
         <v>45477500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>40203700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>36845600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>34918000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>31065100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>30504000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>26796200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>23507800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>22010500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21168300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>17240700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15898700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15567500</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4938,374 +5039,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>6228600</v>
+      </c>
+      <c r="E47" s="3">
         <v>5964200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>8478000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>8682200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5253500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7090400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2064400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5716300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4243400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4897800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4213300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3976300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8181400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7068300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>78469900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>79298300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>70912200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>73349400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>74597900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>74571100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>76920200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>78334800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>85747100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>86364700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>89696300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>91378000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>126676500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>125114900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>128110200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>114262100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>102335700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>101767100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>96187200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>97801300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>98868900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>94302200</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>82258300</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>81415900</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>84238100</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>82166200</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E48" s="3">
         <v>26200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>26800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>27200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>27500</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K48" s="3">
         <v>3700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5200</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N48" s="3">
+      <c r="N48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O48" s="3">
         <v>6700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>9200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>9900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>12500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>669500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>804400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>760600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>766900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>741400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>741900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>750300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>751900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>654600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>660100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>386600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>480100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>486000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>470900</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>474500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>462800</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>474600</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>500000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4201600</v>
+      </c>
+      <c r="E49" s="3">
         <v>4149300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3681200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3519400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3289300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3281600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2918600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2703100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2796400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2662700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2134300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2247600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2034100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1806900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>16700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>17400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>18200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>23100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>24200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>25400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>26500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>37300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>127300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>136900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>137700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>98300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>92800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>94900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>96600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>98600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>100900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>103000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>91000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>92800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>95000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>97600</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>100500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>103300</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>106000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>111700</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5426,8 +5539,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5548,77 +5664,80 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>83674200</v>
+      </c>
+      <c r="E52" s="3">
         <v>82830400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>83131200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>76787500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>68572500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>63578100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>68069500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>66296700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>63116600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>61907400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>65711300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>66177200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>63208900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>62381100</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>11400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>97400</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
-      </c>
       <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
         <v>194100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>238000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3302000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4400700</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>8</v>
       </c>
@@ -5634,8 +5753,8 @@
       <c r="AD52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE52" s="3">
-        <v>0</v>
+      <c r="AE52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF52" s="3">
         <v>0</v>
@@ -5670,8 +5789,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5792,130 +5914,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>143741200</v>
+      </c>
+      <c r="E54" s="3">
         <v>138537600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>135609800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>125861600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>112141900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>105115300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>103556400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>101516000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>93668600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>91483500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>93227200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>89648400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>89330500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>86832000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>81850700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>85406800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>73637200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>76185100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>76764100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>76662400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>82376300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>85369600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>88455100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>89192400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>93458700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>96917300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>130295100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>128956100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>131800800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>119172500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>105787500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>105961800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>98833000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>100382200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>101760100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>97574200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>84976600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>84659000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>87905000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>86909300</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5958,8 +6086,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6002,53 +6131,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>331600</v>
+      </c>
+      <c r="E57" s="3">
         <v>1522800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2059400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2604300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1538500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2304800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>308300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1885300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1096300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2556800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3249400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2214300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4331300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3259000</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6107,314 +6237,323 @@
         <v>0</v>
       </c>
       <c r="AK57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL57" s="3">
         <v>207800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>121200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>84900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>161400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>184300</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>115600</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>87482300</v>
+      </c>
+      <c r="E58" s="3">
         <v>85303600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>84041100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>77732600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>69407500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>64406700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>68219100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>66348400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>62763800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>61205800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>64636600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>62537200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>61795800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>61469600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>59512600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>54160700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>51364100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>52626500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>54769600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>55475400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>60221100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>61202500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>64641200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>64633400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>67163600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>72580200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>101740700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>102595300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>105093500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>88476200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>80581700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>78691200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>75760700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>78015400</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>77696300</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>69430300</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>62497400</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>62719100</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>65215800</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>61784100</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>562900</v>
+      </c>
+      <c r="E59" s="3">
         <v>511200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>494900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>476700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>449500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>421600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>375900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>362700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>325700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>325300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>325100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>321600</v>
-      </c>
-      <c r="O59" s="3">
-        <v>321000</v>
       </c>
       <c r="P59" s="3">
         <v>321000</v>
       </c>
       <c r="Q59" s="3">
+        <v>321000</v>
+      </c>
+      <c r="R59" s="3">
         <v>1906500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9787800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2453900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2407700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>573900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1014700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>661300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1495000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1400000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1658000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2632200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1562100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1317700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1192100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1698200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>5645000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1548100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3007800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1936600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>723900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1257500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>5801900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1534800</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>828600</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>533700</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>896700</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>88797600</v>
+      </c>
+      <c r="E60" s="3">
         <v>87685200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>86976100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>81098700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>71651800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>67418900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>69171700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>68872800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>64554800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>64438300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>68499000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>65271200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>66588800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>65168100</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6490,199 +6629,205 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>37740600</v>
+      </c>
+      <c r="E61" s="3">
         <v>34333900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>32234600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>29518100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>26806300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>24431600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>21445500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>19888700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>17682000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>15408800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13204200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13535000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10789000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9736600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8795000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8840200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8199400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8401600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7108000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5306000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4540600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4147900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7220400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7396900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8505700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8655100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>10563500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>8894600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>8184600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>8426700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>8575600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>8801500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>6799100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>7044700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>7119000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>7383100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>7536000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>7677700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>7865000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>7858200</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>63200</v>
+      </c>
+      <c r="E62" s="3">
         <v>43500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>87900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>248200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>50400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>30400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>242300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>214500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>168900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>140300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>179000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>165100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>65400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>18300</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
         <v>1200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3600</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
-      </c>
       <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
         <v>155000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>159500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2362700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3319400</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>8</v>
       </c>
@@ -6698,8 +6843,8 @@
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE62" s="3">
-        <v>0</v>
+      <c r="AE62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF62" s="3">
         <v>0</v>
@@ -6734,8 +6879,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6856,8 +7004,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6978,8 +7129,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7100,130 +7254,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>126762800</v>
+      </c>
+      <c r="E66" s="3">
         <v>122211800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>119449900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>110865000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>98667500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>92030800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>90859400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>88976000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>82405700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>79987400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>81882100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>78971400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>77443100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>74923000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>70580300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>74540600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>62610500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>64757900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>63594200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>62964600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>68759200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>71313800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>74446800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>75010200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>79665200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>84213800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>114503100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>113736800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>116098100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>103396300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>91675400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>91011800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>85064400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>86445000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>86894600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>83425400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>72374100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>72018900</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>75336900</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>73655600</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7266,8 +7426,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7388,8 +7549,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7510,8 +7674,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7525,7 +7692,7 @@
         <v>1802500</v>
       </c>
       <c r="G70" s="3">
-        <v>1536600</v>
+        <v>1802500</v>
       </c>
       <c r="H70" s="3">
         <v>1536600</v>
@@ -7582,7 +7749,7 @@
         <v>1536600</v>
       </c>
       <c r="Z70" s="3">
-        <v>1982000</v>
+        <v>1536600</v>
       </c>
       <c r="AA70" s="3">
         <v>1982000</v>
@@ -7597,10 +7764,10 @@
         <v>1982000</v>
       </c>
       <c r="AE70" s="3">
+        <v>1982000</v>
+      </c>
+      <c r="AF70" s="3">
         <v>2110300</v>
-      </c>
-      <c r="AF70" s="3">
-        <v>1778200</v>
       </c>
       <c r="AG70" s="3">
         <v>1778200</v>
@@ -7609,19 +7776,19 @@
         <v>1778200</v>
       </c>
       <c r="AI70" s="3">
-        <v>1723200</v>
+        <v>1778200</v>
       </c>
       <c r="AJ70" s="3">
         <v>1723200</v>
       </c>
       <c r="AK70" s="3">
-        <v>1720400</v>
+        <v>1723200</v>
       </c>
       <c r="AL70" s="3">
         <v>1720400</v>
       </c>
       <c r="AM70" s="3">
-        <v>1200600</v>
+        <v>1720400</v>
       </c>
       <c r="AN70" s="3">
         <v>1200600</v>
@@ -7632,8 +7799,11 @@
       <c r="AP70" s="3">
         <v>1200600</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>1200600</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7754,130 +7924,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-13213900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-13429600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-13157300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-13627000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-13942300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-13509900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-13173100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-13238300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-12898200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-12523800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-12622800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-11855300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-10933000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-10741900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-9543200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-8211400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-7496100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-7980400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-9653600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-9720300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-9892900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-9251800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-10667400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-11200900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-11871900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-12382600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-8309400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-9125900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-7982600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-5809900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-4493700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-1812000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-1800400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-2015600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-2961700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-3320200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-3339200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-3024700</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-3136000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>-4655400</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7998,8 +8174,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8120,8 +8299,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8242,130 +8424,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15122900</v>
+      </c>
+      <c r="E76" s="3">
         <v>14471600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14288300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13108400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11844700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11458100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11072700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10906700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9644600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9873000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9719200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9027900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10239700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10255600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9733900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9329600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9490200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9890700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11633300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12161200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12080500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12519200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12471700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12200200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11811400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>10721400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13810000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13237300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13592300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>13998000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12333900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>13171800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12045400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>12214100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>13145100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>12428400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>11402000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>11439500</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>11367600</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>12053100</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8486,257 +8674,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>822700</v>
+      </c>
+      <c r="E81" s="3">
         <v>282700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1013500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>832400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>57100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>124200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>482100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>66400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>462900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-403700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-562200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>167000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-844300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-918300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-302100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>839800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1995400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>388600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>492400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-322500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1723900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>841700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>980200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2855100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3675800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1174200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-783200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1808800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-881600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-2287400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>353900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>564500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1294000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>714600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>337200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-8800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>417000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1825100</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>708400</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8779,130 +8976,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E83" s="3">
         <v>8500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>6400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>9300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>8400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>13200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>11300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>16900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>7700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>7500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>7600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>9500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>7100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>8500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>50900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>7100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>5800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>8500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>9300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>10100</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>9300</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>7800</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9023,8 +9224,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9145,8 +9349,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9267,8 +9474,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9389,8 +9599,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9511,130 +9724,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1619500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1401400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>644300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>24100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>180700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-156300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2808500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1672800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>477100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1697900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>378500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1871000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1136600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1019000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>201600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2454000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>687700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2029100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>861600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>644200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>506500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1064600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>867800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1000500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1340300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-2023300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1195800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-709300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-744000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-942100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-401100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>733100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>957100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1332900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1977700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>4841900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-64900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>177600</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>6022700</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-1032700</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9677,8 +9896,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9721,86 +9941,89 @@
       <c r="P91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R91" s="3">
         <v>-142600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-182800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-263000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-421000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-57400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-317200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-680700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-180100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-168700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-269500</v>
       </c>
-      <c r="AG91" s="3">
-        <v>0</v>
-      </c>
       <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
         <v>99800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-266500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-91600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-78900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-214600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-7800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-259400</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-113600</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-142700</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9921,8 +10144,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10043,130 +10269,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6221400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4395700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9893300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11819800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7312600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1663000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6250100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4429000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4139200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-166500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1203200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5372200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3166000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1080800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5533500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6944400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-418000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1631100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1445000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>3571900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>330100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>2442400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>149900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>1779700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>38422200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>34104500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-876100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>3250300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-15111900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-7904000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-488900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1493100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>2019500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-945900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-9240200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-8219300</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>258300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>2535200</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-4269400</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>2148900</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10209,8 +10441,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10253,86 +10486,89 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R96" s="3">
         <v>-411800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-354100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-321500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-321200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-319000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-317800</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-307700</v>
       </c>
       <c r="X96" s="3">
         <v>-307700</v>
       </c>
       <c r="Y96" s="3">
+        <v>-307700</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-308700</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-309700</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-715200</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-357600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-294900</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-428800</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-434400</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-394300</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-103000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-612800</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-379300</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-381600</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-367100</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-327800</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-329200</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-329100</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-293300</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-333500</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10453,8 +10689,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10575,8 +10814,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10697,130 +10939,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5601600</v>
+      </c>
+      <c r="E100" s="3">
         <v>5671800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>9190100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>11833600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>7357200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1161300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3369500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6074800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3583900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1278200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1410700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3505500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1472100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2317300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>5442500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>5102600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-371600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-784300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>879300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-4550300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-578900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-3627900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1014000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2934100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-37538700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-31108400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-262900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2729400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>16315600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>8632900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1543100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>707400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2825600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-109300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>8176200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>7594600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-537100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-3033100</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-2595800</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-1469300</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10863,8 +11111,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10941,126 +11189,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>999600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-125400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-58900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>37900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>225300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>345500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-72100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-26900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-78300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>253200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>171000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-557300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>217500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>110500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>612200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-101900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-386300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>295800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-334200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>257700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-120900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>3700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-153900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-456800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>972800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>56800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-188400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>459700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-213100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>653000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-52600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>151100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>277700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-161300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>167100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-118700</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-720300</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-842400</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-353100</v>
       </c>
     </row>
